--- a/docs/teste-usabilidade-resultados.xlsx
+++ b/docs/teste-usabilidade-resultados.xlsx
@@ -97,7 +97,7 @@
     <t>T4 — Cadastrar uma experiência da D2 e conferir a memória de cálculo</t>
   </si>
   <si>
-    <t>T5 — Homologar a proposta e gerar a minuta da ata</t>
+    <t>T5 — Concluir a proposta e gerar a minuta da ata</t>
   </si>
   <si>
     <t>Q1</t>
